--- a/data/trans_bre/IP2005-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP2005-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,76; 11,82</t>
+          <t>-5,88; 12,25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,83; 12,64</t>
+          <t>-5,08; 13,09</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 17,68</t>
+          <t>-0,22; 18,13</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 21,36</t>
+          <t>-1,71; 21,23</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,91; 15,57</t>
+          <t>-7,0; 16,08</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,45; 16,11</t>
+          <t>-5,96; 16,81</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,14; 22,84</t>
+          <t>-0,24; 23,92</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 29,67</t>
+          <t>-1,72; 29,31</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,26; 1,56</t>
+          <t>-5,41; 1,65</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,3; 2,36</t>
+          <t>-4,16; 2,72</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 4,21</t>
+          <t>-2,03; 4,13</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 3,61</t>
+          <t>-4,2; 3,63</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-5,81; 1,79</t>
+          <t>-5,95; 1,88</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-4,72; 2,68</t>
+          <t>-4,54; 3,1</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 4,68</t>
+          <t>-2,22; 4,6</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-4,37; 4,13</t>
+          <t>-4,59; 4,17</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 8,73</t>
+          <t>-1,46; 8,71</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,99; 1,73</t>
+          <t>-6,48; 1,53</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 6,16</t>
+          <t>-2,32; 5,68</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-10,43; 2,75</t>
+          <t>-10,61; 2,65</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 10,13</t>
+          <t>-1,57; 9,86</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,11; 1,82</t>
+          <t>-6,66; 1,62</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 6,8</t>
+          <t>-2,39; 6,26</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-11,79; 3,29</t>
+          <t>-11,75; 3,14</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 2,52</t>
+          <t>-2,95; 2,71</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 2,06</t>
+          <t>-3,01; 2,29</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 4,45</t>
+          <t>-0,29; 4,47</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,66; 2,89</t>
+          <t>-3,2; 3,17</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 2,89</t>
+          <t>-3,3; 3,08</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-3,33; 2,29</t>
+          <t>-3,33; 2,54</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 5,0</t>
+          <t>-0,3; 5,04</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-4,1; 3,31</t>
+          <t>-3,59; 3,71</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP2005-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP2005-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,88; 12,25</t>
+          <t>-7,11; 11,75</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,08; 13,09</t>
+          <t>-5,93; 11,63</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 18,13</t>
+          <t>-0,44; 18,07</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 21,23</t>
+          <t>-2,31; 22,21</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,0; 16,08</t>
+          <t>-8,0; 15,52</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,96; 16,81</t>
+          <t>-6,63; 14,8</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 23,92</t>
+          <t>-0,25; 23,69</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 29,31</t>
+          <t>-2,78; 31,49</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,41; 1,65</t>
+          <t>-5,75; 1,56</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 2,72</t>
+          <t>-4,38; 2,47</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 4,13</t>
+          <t>-1,85; 4,3</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,2; 3,63</t>
+          <t>-3,56; 4,03</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-5,95; 1,88</t>
+          <t>-6,35; 1,75</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 3,1</t>
+          <t>-4,71; 2,78</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 4,6</t>
+          <t>-1,97; 4,83</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 4,17</t>
+          <t>-3,92; 4,61</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 8,71</t>
+          <t>-1,27; 8,22</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,48; 1,53</t>
+          <t>-6,17; 2,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 5,68</t>
+          <t>-2,47; 5,93</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-10,61; 2,65</t>
+          <t>-10,72; 2,51</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 9,86</t>
+          <t>-1,47; 9,29</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,66; 1,62</t>
+          <t>-6,32; 2,24</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 6,26</t>
+          <t>-2,52; 6,49</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-11,75; 3,14</t>
+          <t>-11,96; 3,01</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 2,71</t>
+          <t>-2,88; 2,93</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 2,29</t>
+          <t>-3,36; 2,13</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 4,47</t>
+          <t>-0,34; 4,7</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 3,17</t>
+          <t>-3,41; 3,23</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 3,08</t>
+          <t>-3,17; 3,36</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-3,33; 2,54</t>
+          <t>-3,63; 2,37</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 5,04</t>
+          <t>-0,37; 5,25</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 3,71</t>
+          <t>-3,82; 3,74</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP2005-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP2005-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9,82</t>
+          <t>9,44</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>11,92%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,11; 11,75</t>
+          <t>-6,76; 11,82</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,93; 11,63</t>
+          <t>-4,83; 12,64</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 18,07</t>
+          <t>-0,44; 17,68</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 22,21</t>
+          <t>-3,71; 21,86</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-8,0; 15,52</t>
+          <t>-7,91; 15,57</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-6,63; 14,8</t>
+          <t>-5,45; 16,11</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 23,69</t>
+          <t>0,14; 22,84</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 31,49</t>
+          <t>-4,16; 31,96</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-0,16</t>
+          <t>-0,88</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-0,17%</t>
+          <t>-0,99%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,75; 1,56</t>
+          <t>-5,26; 1,56</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,38; 2,47</t>
+          <t>-4,3; 2,36</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 4,3</t>
+          <t>-2,22; 4,21</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 4,03</t>
+          <t>-4,5; 3,03</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-6,35; 1,75</t>
+          <t>-5,81; 1,79</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-4,71; 2,78</t>
+          <t>-4,72; 2,68</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 4,83</t>
+          <t>-2,38; 4,68</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 4,61</t>
+          <t>-4,92; 3,44</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-4,09</t>
+          <t>-3,81</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-4,7%</t>
+          <t>-4,37%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 8,22</t>
+          <t>-1,32; 8,73</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,17; 2,12</t>
+          <t>-5,99; 1,73</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 5,93</t>
+          <t>-2,44; 6,16</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-10,72; 2,51</t>
+          <t>-10,33; 3,01</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 9,29</t>
+          <t>-1,37; 10,13</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,32; 2,24</t>
+          <t>-6,11; 1,82</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 6,49</t>
+          <t>-2,54; 6,8</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-11,96; 3,01</t>
+          <t>-11,66; 3,47</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-0,2</t>
+          <t>-0,75</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-0,23%</t>
+          <t>-0,85%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 2,93</t>
+          <t>-2,78; 2,52</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 2,13</t>
+          <t>-3,06; 2,06</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 4,7</t>
+          <t>-0,36; 4,45</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,41; 3,23</t>
+          <t>-4,24; 2,24</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 3,36</t>
+          <t>-3,08; 2,89</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 2,37</t>
+          <t>-3,33; 2,29</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 5,25</t>
+          <t>-0,34; 5,0</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 3,74</t>
+          <t>-4,75; 2,62</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP2005-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP2005-Estudios-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>2,44</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>3,5</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>9,06</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>9,44</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2,99%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>4,15%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>10,81%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>11,92%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>2.443480380670349</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>3.498181978868631</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>9.059640752760235</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>9.435159306912499</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.0299021716878655</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>0.04150278908049041</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>0.1081476686848702</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>0.1192071616493499</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-6,76; 11,82</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-4,83; 12,64</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-0,44; 17,68</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-3,71; 21,86</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-7,91; 15,57</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-5,45; 16,11</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>0,14; 22,84</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-4,16; 31,96</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-6.756071955078522</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-4.825397571050976</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-0.4444172841273868</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-3.706730086677486</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.07909070761738334</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.05447527990119981</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>0.001405256520448745</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.04157463840126116</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>11.82032187862</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>12.64304975473373</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>17.68203358742373</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>21.86189775719312</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.1557205754851927</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.1610766172104141</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>0.228358209815789</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>0.3196074475053325</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Secundarios</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-2,02</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-0,87</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1,14</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-0,88</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-2,25%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-0,96%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>1,25%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-0,99%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-5,26; 1,56</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-4,3; 2,36</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-2,22; 4,21</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-4,5; 3,03</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-5,81; 1,79</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-4,72; 2,68</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-2,38; 4,68</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-4,92; 3,44</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-2.015384147744115</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-0.8693160345529694</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>1.144475192328342</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-0.8841089215296249</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.02251993403421902</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.009631598018308382</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>0.01253967994220677</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.009903905523062579</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>3,5</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-1,93</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1,71</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-3,81</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>3,83%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-2,01%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>1,82%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-4,37%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-5.255668248947734</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-4.300699751479792</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-2.216848513138904</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-4.497689770043456</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.05808924124831766</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.0471912773890676</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.0237611311822688</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.04916415795725204</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-1,32; 8,73</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-5,99; 1,73</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-2,44; 6,16</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-10,33; 3,01</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-1,37; 10,13</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-6,11; 1,82</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-2,54; 6,8</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-11,66; 3,47</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>1.561353150763438</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>2.358989325974727</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>4.206030898790372</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>3.030338678365205</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.01791364638387787</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.02683486517138316</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.04682570736977369</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.03436893420670993</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,97 +819,197 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-0,08</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-0,56</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2,04</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-0,75</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-0,09%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-0,62%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2,24%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-0,85%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>3.495482080499479</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-1.93130615703262</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>1.706076276864155</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-3.807883503101717</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0.03834721539338102</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.02005709196271475</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>0.01817449784377338</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>-0.04372941942476347</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-2,78; 2,52</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-3,06; 2,06</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-0,36; 4,45</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-4,24; 2,24</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-3,08; 2,89</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-3,33; 2,29</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-0,34; 5,0</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-4,75; 2,62</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-1.315239979793545</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-5.989717850743335</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-2.442737152974308</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-10.32649693684696</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.01374010696231897</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.06106684381275881</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.02541671837697895</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.1165686429193381</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>8.732963973577595</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>1.726828365475405</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>6.158274836151288</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>3.01344992426915</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.1013338635077723</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.01821698404754058</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>0.06798624496662735</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>0.03466149733341045</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-0.07881450075278851</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-0.5638719262789915</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>2.04432851766766</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-0.7514587460370259</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.0008863863938396021</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.006203350489311054</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0.02241949120713237</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.008546209031443599</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-2.7844797684781</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-3.06492289794845</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-0.359802305542555</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-4.238287025570562</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.0307632604337892</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.03330147362946348</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.003430869012643234</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.0475466750503826</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>2.517725118495037</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>2.060179274389097</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>4.449262631310874</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>2.24115846452521</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.02886778695974426</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.02294076384562578</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.04995044099371614</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.0262079221642335</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1008,13 +1017,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
